--- a/LISTAS_ORDENADAS/MI/Tarugos/TARUGO YESO DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tarugos/TARUGO YESO DISMAY.xlsx
@@ -807,14 +807,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45203.55244642433</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="25">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -866,12 +862,6 @@
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="11" t="n"/>
       <c r="B19" s="11" t="n"/>
@@ -879,13 +869,6 @@
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="25">
       <c r="A27" s="17" t="inlineStr">
         <is>
@@ -936,9 +919,6 @@
         <v>16946.6</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="18" customHeight="1" s="25">
       <c r="A33" s="12" t="inlineStr">
         <is>
@@ -965,8 +945,6 @@
     <row r="37" ht="19.5" customHeight="1" s="25">
       <c r="A37" s="13" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -974,18 +952,9 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="19.5" customHeight="1" s="25">
       <c r="A43" s="13" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
     <row r="51" ht="15.75" customHeight="1" s="25">
       <c r="A51" s="3" t="n"/>
     </row>
@@ -994,12 +963,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A9:D9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
